--- a/CSV/Bastion.xlsx
+++ b/CSV/Bastion.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\friend-zone\XLSX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/CSV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177A4053-8EEE-47CC-8C7F-813239FCD8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC375C73-EADC-044A-8128-BAF6BE56BBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="10400" windowHeight="17520" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,29 +34,20 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
-  <si>
-    <t>nummer</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Z</t>
-  </si>
-  <si>
-    <t>/tp</t>
   </si>
   <si>
     <t>x</t>
   </si>
   <si>
-    <t>Y</t>
+    <t>Bastion</t>
   </si>
 </sst>
 </file>
@@ -441,113 +432,1054 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C94"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
+      <c r="B2">
+        <v>3072</v>
       </c>
       <c r="C2">
-        <v>-3347</v>
-      </c>
-      <c r="D2">
-        <v>71</v>
-      </c>
-      <c r="E2">
-        <v>-2979</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>2</v>
+      <c r="B3">
+        <v>3008</v>
       </c>
       <c r="C3">
-        <v>-3246</v>
-      </c>
-      <c r="D3">
-        <v>112</v>
-      </c>
-      <c r="E3">
-        <v>-2606</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-304</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>2</v>
+      <c r="B4">
+        <v>2992</v>
       </c>
       <c r="C4">
-        <v>-3476</v>
-      </c>
-      <c r="D4">
-        <v>102</v>
-      </c>
-      <c r="E4">
-        <v>-1589</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>2</v>
+      <c r="B5">
+        <v>2928</v>
       </c>
       <c r="C5">
-        <v>793</v>
-      </c>
-      <c r="D5">
-        <v>82</v>
-      </c>
-      <c r="E5">
-        <v>2915</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>2</v>
+      <c r="B6">
+        <v>2784</v>
       </c>
       <c r="C6">
-        <v>776</v>
-      </c>
-      <c r="D6">
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2752</v>
+      </c>
+      <c r="C7">
+        <v>-2688</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2736</v>
+      </c>
+      <c r="C8">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2624</v>
+      </c>
+      <c r="C9">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2576</v>
+      </c>
+      <c r="C10">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>2544</v>
+      </c>
+      <c r="C11">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>2416</v>
+      </c>
+      <c r="C12">
+        <v>-1536</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>2304</v>
+      </c>
+      <c r="C13">
+        <v>-2992</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>2080</v>
+      </c>
+      <c r="C14">
+        <v>-2704</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>2064</v>
+      </c>
+      <c r="C15">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>2032</v>
+      </c>
+      <c r="C16">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>2000</v>
+      </c>
+      <c r="C17">
+        <v>-1648</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>1952</v>
+      </c>
+      <c r="C18">
+        <v>-2032</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>1952</v>
+      </c>
+      <c r="C19">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>1808</v>
+      </c>
+      <c r="C20">
+        <v>-1584</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>1728</v>
+      </c>
+      <c r="C21">
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>1632</v>
+      </c>
+      <c r="C22">
+        <v>-2336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>1584</v>
+      </c>
+      <c r="C23">
+        <v>-1104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>1584</v>
+      </c>
+      <c r="C24">
+        <v>-944</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>1568</v>
+      </c>
+      <c r="C25">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>1568</v>
+      </c>
+      <c r="C26">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>1488</v>
+      </c>
+      <c r="C27">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>1360</v>
+      </c>
+      <c r="C28">
+        <v>-880</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>1328</v>
+      </c>
+      <c r="C29">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>1248</v>
+      </c>
+      <c r="C30">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>1232</v>
+      </c>
+      <c r="C31">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>1008</v>
+      </c>
+      <c r="C32">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>1008</v>
+      </c>
+      <c r="C33">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>976</v>
+      </c>
+      <c r="C34">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>848</v>
+      </c>
+      <c r="C35">
+        <v>-1408</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>816</v>
+      </c>
+      <c r="C36">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>704</v>
+      </c>
+      <c r="C37">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>688</v>
+      </c>
+      <c r="C38">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>688</v>
+      </c>
+      <c r="C39">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>656</v>
+      </c>
+      <c r="C40">
+        <v>-672</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>640</v>
+      </c>
+      <c r="C41">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>576</v>
+      </c>
+      <c r="C42">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>288</v>
+      </c>
+      <c r="C43">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>240</v>
+      </c>
+      <c r="C44">
+        <v>-2496</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>208</v>
+      </c>
+      <c r="C45">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>160</v>
+      </c>
+      <c r="C46">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>144</v>
+      </c>
+      <c r="C47">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>128</v>
+      </c>
+      <c r="C48">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>112</v>
+      </c>
+      <c r="C49">
+        <v>-1744</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>64</v>
+      </c>
+      <c r="C50">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>-176</v>
+      </c>
+      <c r="C51">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>-224</v>
+      </c>
+      <c r="C52">
+        <v>-2736</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>-224</v>
+      </c>
+      <c r="C53">
+        <v>-2400</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>-288</v>
+      </c>
+      <c r="C54">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>-304</v>
+      </c>
+      <c r="C55">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>-320</v>
+      </c>
+      <c r="C56">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>-400</v>
+      </c>
+      <c r="C57">
+        <v>-1168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>-592</v>
+      </c>
+      <c r="C58">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>-640</v>
+      </c>
+      <c r="C59">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>-656</v>
+      </c>
+      <c r="C60">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>-784</v>
+      </c>
+      <c r="C61">
+        <v>-1408</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>-880</v>
+      </c>
+      <c r="C62">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>-1200</v>
+      </c>
+      <c r="C63">
+        <v>-1872</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>-1216</v>
+      </c>
+      <c r="C64">
+        <v>-1056</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>-1216</v>
+      </c>
+      <c r="C65">
+        <v>-576</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>-1232</v>
+      </c>
+      <c r="C66">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>-1248</v>
+      </c>
+      <c r="C67">
+        <v>-256</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>-1312</v>
+      </c>
+      <c r="C68">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>-1424</v>
+      </c>
+      <c r="C69">
+        <v>-2736</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>-1424</v>
+      </c>
+      <c r="C70">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>-1520</v>
+      </c>
+      <c r="C71">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>-1600</v>
+      </c>
+      <c r="C72">
+        <v>-1584</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>-1632</v>
+      </c>
+      <c r="C73">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>-1696</v>
+      </c>
+      <c r="C74">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>-1696</v>
+      </c>
+      <c r="C75">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>-1744</v>
+      </c>
+      <c r="C76">
+        <v>-2816</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>-1792</v>
+      </c>
+      <c r="C77">
+        <v>-352</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>-1920</v>
+      </c>
+      <c r="C78">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>-2000</v>
+      </c>
+      <c r="C79">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>-2112</v>
+      </c>
+      <c r="C80">
+        <v>-2720</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>-2160</v>
+      </c>
+      <c r="C81">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>-2192</v>
+      </c>
+      <c r="C82">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>-2320</v>
+      </c>
+      <c r="C83">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>-2496</v>
+      </c>
+      <c r="C84">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85">
         <v>84</v>
       </c>
-      <c r="E6">
-        <v>2906</v>
+      <c r="B85">
+        <v>-2512</v>
+      </c>
+      <c r="C85">
+        <v>-2624</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>-2576</v>
+      </c>
+      <c r="C86">
+        <v>-1776</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>-2576</v>
+      </c>
+      <c r="C87">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>-2592</v>
+      </c>
+      <c r="C88">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>-2624</v>
+      </c>
+      <c r="C89">
+        <v>-384</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>-2624</v>
+      </c>
+      <c r="C90">
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>-2640</v>
+      </c>
+      <c r="C91">
+        <v>-896</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>-2736</v>
+      </c>
+      <c r="C92">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>-2800</v>
+      </c>
+      <c r="C93">
+        <v>-3040</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>-2864</v>
+      </c>
+      <c r="C94">
+        <v>-2272</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}"/>
+  <autoFilter ref="A1:C1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C94">
+      <sortCondition descending="1" ref="B1:B94"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
